--- a/artfynd/A 27675-2023 artfynd.xlsx
+++ b/artfynd/A 27675-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27675-2023 artfynd.xlsx
+++ b/artfynd/A 27675-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1949,122 +1949,6 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>105935541</v>
-      </c>
-      <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Sträckningen Betåsen - Nässe, Ång</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>587970.4954503796</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7045373.039638958</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Ådals-Liden</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27675-2023 artfynd.xlsx
+++ b/artfynd/A 27675-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105935539</v>
+        <v>105934843</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587964.5500405186</v>
+        <v>587945</v>
       </c>
       <c r="R2" t="n">
-        <v>7045361.714430304</v>
+        <v>7045347</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105934843</v>
+        <v>105935680</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587944.8557014973</v>
+        <v>587945</v>
       </c>
       <c r="R3" t="n">
-        <v>7045346.437725567</v>
+        <v>7045346</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +848,9 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,16 +880,11 @@
         <v>105935681</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -951,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587991.4298995794</v>
+        <v>587991</v>
       </c>
       <c r="R4" t="n">
-        <v>7045311.117013589</v>
+        <v>7045311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,19 +949,9 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105935540</v>
+        <v>105935682</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587971.3641688843</v>
+        <v>588003</v>
       </c>
       <c r="R5" t="n">
-        <v>7045373.956520522</v>
+        <v>7045308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,19 +1050,9 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105935542</v>
+        <v>105935683</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587970.5571063366</v>
+        <v>588006</v>
       </c>
       <c r="R6" t="n">
-        <v>7045370.809172779</v>
+        <v>7045323</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1151,9 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,16 +1183,11 @@
         <v>105935684</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1299,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588015.0334871619</v>
+        <v>588015</v>
       </c>
       <c r="R7" t="n">
-        <v>7045330.520252334</v>
+        <v>7045330</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,19 +1252,9 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,12 +1284,7 @@
         <v>105935475</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587980.584343765</v>
+        <v>587980</v>
       </c>
       <c r="R8" t="n">
-        <v>7045380.015041471</v>
+        <v>7045380</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,19 +1353,9 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,12 +1385,7 @@
         <v>105934913</v>
       </c>
       <c r="B9" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587980.584343765</v>
+        <v>587980</v>
       </c>
       <c r="R9" t="n">
-        <v>7045380.015041471</v>
+        <v>7045380</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,19 +1454,9 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105935683</v>
+        <v>105935539</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588006.2845975674</v>
+        <v>587965</v>
       </c>
       <c r="R10" t="n">
-        <v>7045323.58169317</v>
+        <v>7045362</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,19 +1555,9 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105935680</v>
+        <v>105935540</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1763,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587944.880356636</v>
+        <v>587972</v>
       </c>
       <c r="R11" t="n">
-        <v>7045345.54553189</v>
+        <v>7045374</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,19 +1656,9 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,37 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105935682</v>
+        <v>105935541</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1879,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588003.1304302386</v>
+        <v>587971</v>
       </c>
       <c r="R12" t="n">
-        <v>7045308.31543636</v>
+        <v>7045373</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1912,19 +1757,9 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,6 +1783,107 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>105935542</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sträckningen Betåsen - Nässe, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>587970</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7045371</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-06-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-06-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27675-2023 artfynd.xlsx
+++ b/artfynd/A 27675-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105934843</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935680</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935681</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935682</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935683</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935684</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935475</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105934913</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935539</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935540</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935541</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,8 +1944,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935542</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>